--- a/데이터/opened_course2025_1.xlsx
+++ b/데이터/opened_course2025_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d90a49386c3f612/바탕 화면/AI융개_팀플/데이터/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{ACEFED3B-ADB4-4921-83B8-55788854BB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E25417CB-AFE9-477E-B569-1933BEC144A5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD72840-DE4E-43E9-9EF7-2C6E0DBD6A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="심화전공2025_1" sheetId="4" r:id="rId1"/>
@@ -19,12 +19,11 @@
     <sheet name="공통교양2025_1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="481">
   <si>
     <t>수리통계데이터사이언스학부</t>
   </si>
@@ -712,10 +711,6 @@
   </si>
   <si>
     <t>인문융합예술대학</t>
-  </si>
-  <si>
-    <t>개설과목전공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>핵심전공</t>
@@ -1892,13 +1887,13 @@
         <v>218</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1909,13 +1904,13 @@
         <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1926,13 +1921,13 @@
         <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1943,13 +1938,13 @@
         <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1960,13 +1955,13 @@
         <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1977,13 +1972,13 @@
         <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1994,13 +1989,13 @@
         <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -2011,13 +2006,13 @@
         <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -2028,13 +2023,13 @@
         <v>217</v>
       </c>
       <c r="B10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2045,13 +2040,13 @@
         <v>217</v>
       </c>
       <c r="B11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -2062,13 +2057,13 @@
         <v>217</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2079,13 +2074,13 @@
         <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -2096,13 +2091,13 @@
         <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -2113,13 +2108,13 @@
         <v>217</v>
       </c>
       <c r="B15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -2130,13 +2125,13 @@
         <v>217</v>
       </c>
       <c r="B16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2147,13 +2142,13 @@
         <v>217</v>
       </c>
       <c r="B17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2164,13 +2159,13 @@
         <v>217</v>
       </c>
       <c r="B18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -2181,13 +2176,13 @@
         <v>217</v>
       </c>
       <c r="B19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -2198,13 +2193,13 @@
         <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -2215,13 +2210,13 @@
         <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -2232,13 +2227,13 @@
         <v>216</v>
       </c>
       <c r="B22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -2249,13 +2244,13 @@
         <v>216</v>
       </c>
       <c r="B23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -2266,13 +2261,13 @@
         <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -2283,13 +2278,13 @@
         <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -2300,13 +2295,13 @@
         <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -2317,13 +2312,13 @@
         <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -2334,13 +2329,13 @@
         <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -2351,13 +2346,13 @@
         <v>215</v>
       </c>
       <c r="B29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2368,13 +2363,13 @@
         <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -2385,13 +2380,13 @@
         <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -2402,13 +2397,13 @@
         <v>215</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C32" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D32" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -2419,13 +2414,13 @@
         <v>215</v>
       </c>
       <c r="B33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -2436,13 +2431,13 @@
         <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D34" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -2453,13 +2448,13 @@
         <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -2470,13 +2465,13 @@
         <v>214</v>
       </c>
       <c r="B36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C36" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D36" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -2487,13 +2482,13 @@
         <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C37" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -2504,13 +2499,13 @@
         <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -2521,13 +2516,13 @@
         <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C39" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -2538,13 +2533,13 @@
         <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2555,13 +2550,13 @@
         <v>214</v>
       </c>
       <c r="B41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C41" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -2572,13 +2567,13 @@
         <v>214</v>
       </c>
       <c r="B42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C42" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2589,13 +2584,13 @@
         <v>214</v>
       </c>
       <c r="B43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C43" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -2606,13 +2601,13 @@
         <v>213</v>
       </c>
       <c r="B44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -2623,13 +2618,13 @@
         <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C45" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -2640,13 +2635,13 @@
         <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -2657,13 +2652,13 @@
         <v>213</v>
       </c>
       <c r="B47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D47" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -2674,13 +2669,13 @@
         <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -2691,13 +2686,13 @@
         <v>213</v>
       </c>
       <c r="B49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D49" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -2708,13 +2703,13 @@
         <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -2725,13 +2720,13 @@
         <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C51" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D51" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -2742,13 +2737,13 @@
         <v>213</v>
       </c>
       <c r="B52" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D52" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -2759,13 +2754,13 @@
         <v>213</v>
       </c>
       <c r="B53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C53" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D53" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -2776,13 +2771,13 @@
         <v>213</v>
       </c>
       <c r="B54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D54" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -2793,13 +2788,13 @@
         <v>213</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C55" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D55" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -2810,13 +2805,13 @@
         <v>213</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D56" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -2827,13 +2822,13 @@
         <v>213</v>
       </c>
       <c r="B57" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D57" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -2844,13 +2839,13 @@
         <v>213</v>
       </c>
       <c r="B58" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C58" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D58" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2861,13 +2856,13 @@
         <v>213</v>
       </c>
       <c r="B59" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C59" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D59" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -2878,13 +2873,13 @@
         <v>213</v>
       </c>
       <c r="B60" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C60" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D60" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -2895,13 +2890,13 @@
         <v>213</v>
       </c>
       <c r="B61" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C61" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D61" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -2912,13 +2907,13 @@
         <v>212</v>
       </c>
       <c r="B62" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -2929,13 +2924,13 @@
         <v>212</v>
       </c>
       <c r="B63" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C63" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -2946,13 +2941,13 @@
         <v>212</v>
       </c>
       <c r="B64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C64" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -2963,13 +2958,13 @@
         <v>212</v>
       </c>
       <c r="B65" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -2980,13 +2975,13 @@
         <v>212</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C66" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D66" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -2997,13 +2992,13 @@
         <v>212</v>
       </c>
       <c r="B67" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C67" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D67" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -3014,13 +3009,13 @@
         <v>212</v>
       </c>
       <c r="B68" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D68" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E68">
         <v>3</v>
@@ -3031,13 +3026,13 @@
         <v>211</v>
       </c>
       <c r="B69" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -3048,13 +3043,13 @@
         <v>211</v>
       </c>
       <c r="B70" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -3065,13 +3060,13 @@
         <v>211</v>
       </c>
       <c r="B71" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -3082,13 +3077,13 @@
         <v>211</v>
       </c>
       <c r="B72" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -3099,13 +3094,13 @@
         <v>211</v>
       </c>
       <c r="B73" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -3116,13 +3111,13 @@
         <v>211</v>
       </c>
       <c r="B74" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C74" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -3133,13 +3128,13 @@
         <v>211</v>
       </c>
       <c r="B75" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C75" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -3150,13 +3145,13 @@
         <v>211</v>
       </c>
       <c r="B76" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D76" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -3167,13 +3162,13 @@
         <v>211</v>
       </c>
       <c r="B77" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C77" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -3184,13 +3179,13 @@
         <v>211</v>
       </c>
       <c r="B78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C78" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D78" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -3201,13 +3196,13 @@
         <v>211</v>
       </c>
       <c r="B79" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C79" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D79" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -3218,13 +3213,13 @@
         <v>211</v>
       </c>
       <c r="B80" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -3235,13 +3230,13 @@
         <v>211</v>
       </c>
       <c r="B81" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C81" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D81" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -3252,13 +3247,13 @@
         <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C82" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D82" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -3269,13 +3264,13 @@
         <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C83" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D83" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -3286,13 +3281,13 @@
         <v>211</v>
       </c>
       <c r="B84" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C84" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D84" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -3303,13 +3298,13 @@
         <v>211</v>
       </c>
       <c r="B85" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C85" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D85" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -3320,13 +3315,13 @@
         <v>211</v>
       </c>
       <c r="B86" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C86" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D86" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -3337,13 +3332,13 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C87" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D87" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -3354,13 +3349,13 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C88" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D88" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E88">
         <v>3</v>
@@ -3371,13 +3366,13 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C89" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D89" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E89">
         <v>3</v>
@@ -3388,13 +3383,13 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C90" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D90" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -3405,13 +3400,13 @@
         <v>210</v>
       </c>
       <c r="B91" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C91" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D91" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -3422,13 +3417,13 @@
         <v>210</v>
       </c>
       <c r="B92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C92" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D92" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E92">
         <v>3</v>
@@ -3439,13 +3434,13 @@
         <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C93" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D93" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E93">
         <v>3</v>
@@ -3456,13 +3451,13 @@
         <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C94" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -3473,13 +3468,13 @@
         <v>210</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D95" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E95">
         <v>3</v>
@@ -3490,13 +3485,13 @@
         <v>210</v>
       </c>
       <c r="B96" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -3507,13 +3502,13 @@
         <v>210</v>
       </c>
       <c r="B97" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D97" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -3524,13 +3519,13 @@
         <v>210</v>
       </c>
       <c r="B98" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E98">
         <v>3</v>
@@ -3541,13 +3536,13 @@
         <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C99" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D99" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E99">
         <v>3</v>
@@ -3558,13 +3553,13 @@
         <v>210</v>
       </c>
       <c r="B100" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C100" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D100" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3575,13 +3570,13 @@
         <v>210</v>
       </c>
       <c r="B101" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C101" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D101" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E101">
         <v>3</v>
@@ -3592,13 +3587,13 @@
         <v>209</v>
       </c>
       <c r="B102" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C102" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D102" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E102">
         <v>3</v>
@@ -3609,13 +3604,13 @@
         <v>209</v>
       </c>
       <c r="B103" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E103">
         <v>3</v>
@@ -3626,13 +3621,13 @@
         <v>209</v>
       </c>
       <c r="B104" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C104" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D104" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E104">
         <v>3</v>
@@ -3643,13 +3638,13 @@
         <v>209</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C105" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D105" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E105">
         <v>3</v>
@@ -3660,13 +3655,13 @@
         <v>209</v>
       </c>
       <c r="B106" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C106" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D106" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E106">
         <v>3</v>
@@ -3677,13 +3672,13 @@
         <v>209</v>
       </c>
       <c r="B107" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D107" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E107">
         <v>3</v>
@@ -3694,13 +3689,13 @@
         <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D108" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -3711,13 +3706,13 @@
         <v>209</v>
       </c>
       <c r="B109" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C109" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D109" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E109">
         <v>3</v>
@@ -3728,13 +3723,13 @@
         <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C110" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D110" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E110">
         <v>3</v>
@@ -3745,13 +3740,13 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C111" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D111" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E111">
         <v>3</v>
@@ -3762,13 +3757,13 @@
         <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C112" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D112" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E112">
         <v>3</v>
@@ -3779,13 +3774,13 @@
         <v>209</v>
       </c>
       <c r="B113" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C113" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D113" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E113">
         <v>3</v>
@@ -3796,13 +3791,13 @@
         <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C114" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E114">
         <v>3</v>
@@ -3813,13 +3808,13 @@
         <v>209</v>
       </c>
       <c r="B115" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C115" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D115" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E115">
         <v>3</v>
@@ -3830,13 +3825,13 @@
         <v>209</v>
       </c>
       <c r="B116" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D116" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E116">
         <v>3</v>
@@ -3847,13 +3842,13 @@
         <v>209</v>
       </c>
       <c r="B117" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C117" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D117" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E117">
         <v>3</v>
@@ -3864,13 +3859,13 @@
         <v>208</v>
       </c>
       <c r="B118" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D118" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E118">
         <v>3</v>
@@ -3881,13 +3876,13 @@
         <v>208</v>
       </c>
       <c r="B119" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C119" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D119" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E119">
         <v>3</v>
@@ -3898,13 +3893,13 @@
         <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C120" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D120" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E120">
         <v>3</v>
@@ -3915,13 +3910,13 @@
         <v>208</v>
       </c>
       <c r="B121" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C121" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D121" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E121">
         <v>3</v>
@@ -3932,13 +3927,13 @@
         <v>208</v>
       </c>
       <c r="B122" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C122" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D122" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E122">
         <v>3</v>
@@ -3949,13 +3944,13 @@
         <v>208</v>
       </c>
       <c r="B123" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D123" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E123">
         <v>3</v>
@@ -3966,13 +3961,13 @@
         <v>208</v>
       </c>
       <c r="B124" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C124" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D124" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -3983,13 +3978,13 @@
         <v>208</v>
       </c>
       <c r="B125" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C125" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D125" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E125">
         <v>3</v>
@@ -4000,13 +3995,13 @@
         <v>207</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C126" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D126" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E126">
         <v>3</v>
@@ -4017,13 +4012,13 @@
         <v>207</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C127" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E127">
         <v>3</v>
@@ -4034,13 +4029,13 @@
         <v>207</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C128" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D128" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -4051,13 +4046,13 @@
         <v>207</v>
       </c>
       <c r="B129" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C129" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D129" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E129">
         <v>3</v>
@@ -4068,13 +4063,13 @@
         <v>207</v>
       </c>
       <c r="B130" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C130" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D130" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E130">
         <v>3</v>
@@ -4085,13 +4080,13 @@
         <v>207</v>
       </c>
       <c r="B131" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C131" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D131" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E131">
         <v>3</v>
@@ -4102,13 +4097,13 @@
         <v>207</v>
       </c>
       <c r="B132" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C132" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D132" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E132">
         <v>2</v>
@@ -4119,13 +4114,13 @@
         <v>207</v>
       </c>
       <c r="B133" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C133" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D133" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E133">
         <v>3</v>
@@ -4136,13 +4131,13 @@
         <v>206</v>
       </c>
       <c r="B134" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C134" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D134" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E134">
         <v>3</v>
@@ -4153,13 +4148,13 @@
         <v>206</v>
       </c>
       <c r="B135" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C135" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D135" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E135">
         <v>3</v>
@@ -4170,13 +4165,13 @@
         <v>206</v>
       </c>
       <c r="B136" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C136" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D136" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -4187,13 +4182,13 @@
         <v>206</v>
       </c>
       <c r="B137" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C137" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D137" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E137">
         <v>2</v>
@@ -4204,13 +4199,13 @@
         <v>206</v>
       </c>
       <c r="B138" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D138" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E138">
         <v>3</v>
@@ -4221,13 +4216,13 @@
         <v>206</v>
       </c>
       <c r="B139" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C139" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D139" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -4238,13 +4233,13 @@
         <v>206</v>
       </c>
       <c r="B140" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C140" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D140" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E140">
         <v>2</v>
@@ -4255,13 +4250,13 @@
         <v>206</v>
       </c>
       <c r="B141" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C141" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D141" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E141">
         <v>2</v>
@@ -4272,13 +4267,13 @@
         <v>206</v>
       </c>
       <c r="B142" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C142" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D142" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E142">
         <v>3</v>
@@ -4289,13 +4284,13 @@
         <v>91</v>
       </c>
       <c r="B143" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C143" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D143" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -4306,13 +4301,13 @@
         <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D144" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E144">
         <v>3</v>
@@ -4323,13 +4318,13 @@
         <v>91</v>
       </c>
       <c r="B145" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C145" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E145">
         <v>3</v>
@@ -4340,13 +4335,13 @@
         <v>91</v>
       </c>
       <c r="B146" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C146" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D146" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -4357,13 +4352,13 @@
         <v>91</v>
       </c>
       <c r="B147" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C147" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D147" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -4374,13 +4369,13 @@
         <v>91</v>
       </c>
       <c r="B148" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D148" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -4391,13 +4386,13 @@
         <v>91</v>
       </c>
       <c r="B149" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C149" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D149" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -4408,13 +4403,13 @@
         <v>91</v>
       </c>
       <c r="B150" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C150" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D150" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E150">
         <v>2</v>
@@ -4425,13 +4420,13 @@
         <v>91</v>
       </c>
       <c r="B151" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C151" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D151" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E151">
         <v>3</v>
@@ -4442,13 +4437,13 @@
         <v>205</v>
       </c>
       <c r="B152" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C152" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D152" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E152">
         <v>3</v>
@@ -4459,13 +4454,13 @@
         <v>205</v>
       </c>
       <c r="B153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C153" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D153" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E153">
         <v>3</v>
@@ -4476,13 +4471,13 @@
         <v>205</v>
       </c>
       <c r="B154" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D154" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E154">
         <v>3</v>
@@ -4493,13 +4488,13 @@
         <v>205</v>
       </c>
       <c r="B155" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C155" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D155" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E155">
         <v>2</v>
@@ -4510,13 +4505,13 @@
         <v>205</v>
       </c>
       <c r="B156" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C156" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D156" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E156">
         <v>3</v>
@@ -4527,13 +4522,13 @@
         <v>205</v>
       </c>
       <c r="B157" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C157" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D157" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E157">
         <v>2</v>
@@ -4544,13 +4539,13 @@
         <v>205</v>
       </c>
       <c r="B158" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C158" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D158" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -4561,13 +4556,13 @@
         <v>205</v>
       </c>
       <c r="B159" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C159" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D159" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E159">
         <v>3</v>
@@ -4578,13 +4573,13 @@
         <v>205</v>
       </c>
       <c r="B160" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C160" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D160" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E160">
         <v>3</v>
@@ -4595,13 +4590,13 @@
         <v>204</v>
       </c>
       <c r="B161" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C161" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D161" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E161">
         <v>3</v>
@@ -4612,13 +4607,13 @@
         <v>204</v>
       </c>
       <c r="B162" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C162" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D162" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E162">
         <v>3</v>
@@ -4629,13 +4624,13 @@
         <v>204</v>
       </c>
       <c r="B163" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C163" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D163" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E163">
         <v>3</v>
@@ -4646,13 +4641,13 @@
         <v>204</v>
       </c>
       <c r="B164" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C164" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D164" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E164">
         <v>3</v>
@@ -4663,13 +4658,13 @@
         <v>204</v>
       </c>
       <c r="B165" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C165" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D165" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E165">
         <v>3</v>
@@ -4680,13 +4675,13 @@
         <v>204</v>
       </c>
       <c r="B166" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C166" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D166" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E166">
         <v>3</v>
@@ -4697,13 +4692,13 @@
         <v>204</v>
       </c>
       <c r="B167" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C167" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D167" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E167">
         <v>3</v>
@@ -4714,13 +4709,13 @@
         <v>204</v>
       </c>
       <c r="B168" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C168" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D168" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E168">
         <v>3</v>
@@ -4731,13 +4726,13 @@
         <v>204</v>
       </c>
       <c r="B169" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C169" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D169" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E169">
         <v>3</v>
@@ -4748,13 +4743,13 @@
         <v>204</v>
       </c>
       <c r="B170" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C170" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D170" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E170">
         <v>3</v>
@@ -4765,13 +4760,13 @@
         <v>203</v>
       </c>
       <c r="B171" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C171" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D171" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E171">
         <v>3</v>
@@ -4782,13 +4777,13 @@
         <v>203</v>
       </c>
       <c r="B172" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C172" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D172" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E172">
         <v>3</v>
@@ -4799,13 +4794,13 @@
         <v>203</v>
       </c>
       <c r="B173" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C173" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D173" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E173">
         <v>3</v>
@@ -4816,13 +4811,13 @@
         <v>203</v>
       </c>
       <c r="B174" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C174" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D174" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -4833,13 +4828,13 @@
         <v>203</v>
       </c>
       <c r="B175" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C175" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D175" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E175">
         <v>3</v>
@@ -4850,13 +4845,13 @@
         <v>203</v>
       </c>
       <c r="B176" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C176" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D176" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E176">
         <v>3</v>
@@ -4867,13 +4862,13 @@
         <v>202</v>
       </c>
       <c r="B177" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C177" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D177" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E177">
         <v>3</v>
@@ -4884,13 +4879,13 @@
         <v>202</v>
       </c>
       <c r="B178" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C178" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D178" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E178">
         <v>3</v>
@@ -4901,13 +4896,13 @@
         <v>202</v>
       </c>
       <c r="B179" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C179" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D179" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E179">
         <v>3</v>
@@ -4918,13 +4913,13 @@
         <v>202</v>
       </c>
       <c r="B180" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C180" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D180" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E180">
         <v>3</v>
@@ -4947,7 +4942,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>227</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -4967,13 +4962,13 @@
         <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4984,13 +4979,13 @@
         <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5001,13 +4996,13 @@
         <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5018,13 +5013,13 @@
         <v>225</v>
       </c>
       <c r="B5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5035,13 +5030,13 @@
         <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5052,13 +5047,13 @@
         <v>224</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5069,13 +5064,13 @@
         <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5086,13 +5081,13 @@
         <v>224</v>
       </c>
       <c r="B9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5103,13 +5098,13 @@
         <v>224</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5120,13 +5115,13 @@
         <v>224</v>
       </c>
       <c r="B11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -5137,13 +5132,13 @@
         <v>224</v>
       </c>
       <c r="B12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -5154,13 +5149,13 @@
         <v>223</v>
       </c>
       <c r="B13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -5171,13 +5166,13 @@
         <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -5188,13 +5183,13 @@
         <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -5205,13 +5200,13 @@
         <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -5222,13 +5217,13 @@
         <v>223</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5239,13 +5234,13 @@
         <v>223</v>
       </c>
       <c r="B18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -5256,13 +5251,13 @@
         <v>223</v>
       </c>
       <c r="B19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -5273,13 +5268,13 @@
         <v>222</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -5290,13 +5285,13 @@
         <v>222</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -5307,13 +5302,13 @@
         <v>222</v>
       </c>
       <c r="B22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C22" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -5324,13 +5319,13 @@
         <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -5341,13 +5336,13 @@
         <v>222</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D24" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -5358,13 +5353,13 @@
         <v>222</v>
       </c>
       <c r="B25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -5375,13 +5370,13 @@
         <v>222</v>
       </c>
       <c r="B26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -5392,13 +5387,13 @@
         <v>222</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -5409,13 +5404,13 @@
         <v>222</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -5426,13 +5421,13 @@
         <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -5443,13 +5438,13 @@
         <v>222</v>
       </c>
       <c r="B30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -5460,13 +5455,13 @@
         <v>222</v>
       </c>
       <c r="B31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -5477,13 +5472,13 @@
         <v>221</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -5494,13 +5489,13 @@
         <v>221</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -5511,13 +5506,13 @@
         <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D34" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -5528,13 +5523,13 @@
         <v>221</v>
       </c>
       <c r="B35" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C35" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -5545,13 +5540,13 @@
         <v>221</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -5562,13 +5557,13 @@
         <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -5579,13 +5574,13 @@
         <v>221</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -5596,13 +5591,13 @@
         <v>221</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D39" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -5613,13 +5608,13 @@
         <v>221</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -5630,13 +5625,13 @@
         <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -5647,13 +5642,13 @@
         <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D42" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -5664,13 +5659,13 @@
         <v>221</v>
       </c>
       <c r="B43" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D43" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -5681,13 +5676,13 @@
         <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -5698,13 +5693,13 @@
         <v>220</v>
       </c>
       <c r="B45" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -5715,13 +5710,13 @@
         <v>220</v>
       </c>
       <c r="B46" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D46" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -5732,13 +5727,13 @@
         <v>220</v>
       </c>
       <c r="B47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -5749,13 +5744,13 @@
         <v>220</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -5766,13 +5761,13 @@
         <v>220</v>
       </c>
       <c r="B49" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D49" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -5783,13 +5778,13 @@
         <v>220</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -5800,13 +5795,13 @@
         <v>220</v>
       </c>
       <c r="B51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -5817,13 +5812,13 @@
         <v>220</v>
       </c>
       <c r="B52" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -5834,13 +5829,13 @@
         <v>219</v>
       </c>
       <c r="B53" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D53" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -5851,13 +5846,13 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -5868,13 +5863,13 @@
         <v>219</v>
       </c>
       <c r="B55" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D55" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -5885,13 +5880,13 @@
         <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -5902,13 +5897,13 @@
         <v>219</v>
       </c>
       <c r="B57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -5919,13 +5914,13 @@
         <v>219</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -5936,13 +5931,13 @@
         <v>219</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -5953,13 +5948,13 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D60" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -5970,13 +5965,13 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D61" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -5987,13 +5982,13 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -6004,13 +5999,13 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -6021,13 +6016,13 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -6038,13 +6033,13 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E65">
         <v>3</v>
@@ -6055,13 +6050,13 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C66" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -6072,13 +6067,13 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -6089,13 +6084,13 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E68">
         <v>3</v>
@@ -6106,13 +6101,13 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -6123,13 +6118,13 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -6140,13 +6135,13 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -6157,13 +6152,13 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -6174,13 +6169,13 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D73" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -6191,13 +6186,13 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D74" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -6208,13 +6203,13 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C75" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -6225,13 +6220,13 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D76" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -6242,13 +6237,13 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -6259,13 +6254,13 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C78" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D78" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -6276,13 +6271,13 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C79" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D79" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E79">
         <v>3</v>
@@ -6293,13 +6288,13 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C80" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D80" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E80">
         <v>3</v>
@@ -6310,13 +6305,13 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C81" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D81" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E81">
         <v>3</v>
@@ -6327,13 +6322,13 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D82" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -6344,13 +6339,13 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C83" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D83" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -6361,13 +6356,13 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C84" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D84" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E84">
         <v>3</v>
@@ -6378,13 +6373,13 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C85" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D85" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -6395,13 +6390,13 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C86" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -6412,13 +6407,13 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C87" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D87" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -6429,13 +6424,13 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C88" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E88">
         <v>3</v>
@@ -6446,13 +6441,13 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E89">
         <v>3</v>
@@ -6463,13 +6458,13 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C90" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D90" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E90">
         <v>3</v>
@@ -6480,13 +6475,13 @@
         <v>210</v>
       </c>
       <c r="B91" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C91" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D91" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -6497,13 +6492,13 @@
         <v>210</v>
       </c>
       <c r="B92" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E92">
         <v>3</v>
@@ -6514,13 +6509,13 @@
         <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D93" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E93">
         <v>3</v>
@@ -6531,13 +6526,13 @@
         <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C94" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D94" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -6548,13 +6543,13 @@
         <v>210</v>
       </c>
       <c r="B95" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C95" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D95" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E95">
         <v>3</v>
@@ -6565,13 +6560,13 @@
         <v>210</v>
       </c>
       <c r="B96" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D96" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -6582,13 +6577,13 @@
         <v>210</v>
       </c>
       <c r="B97" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -6599,13 +6594,13 @@
         <v>210</v>
       </c>
       <c r="B98" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C98" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D98" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E98">
         <v>3</v>
@@ -6616,13 +6611,13 @@
         <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D99" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E99">
         <v>3</v>
@@ -6633,13 +6628,13 @@
         <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C100" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D100" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -6650,13 +6645,13 @@
         <v>209</v>
       </c>
       <c r="B101" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C101" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E101">
         <v>3</v>
@@ -6667,13 +6662,13 @@
         <v>209</v>
       </c>
       <c r="B102" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C102" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D102" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E102">
         <v>3</v>
@@ -6684,13 +6679,13 @@
         <v>209</v>
       </c>
       <c r="B103" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C103" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D103" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E103">
         <v>3</v>
@@ -6701,13 +6696,13 @@
         <v>209</v>
       </c>
       <c r="B104" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C104" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D104" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E104">
         <v>3</v>
@@ -6718,13 +6713,13 @@
         <v>208</v>
       </c>
       <c r="B105" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C105" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E105">
         <v>3</v>
@@ -6735,13 +6730,13 @@
         <v>207</v>
       </c>
       <c r="B106" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C106" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D106" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E106">
         <v>2</v>
@@ -6752,13 +6747,13 @@
         <v>207</v>
       </c>
       <c r="B107" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E107">
         <v>2</v>
@@ -6769,13 +6764,13 @@
         <v>207</v>
       </c>
       <c r="B108" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C108" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D108" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E108">
         <v>2</v>
@@ -6786,13 +6781,13 @@
         <v>207</v>
       </c>
       <c r="B109" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C109" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D109" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -6803,13 +6798,13 @@
         <v>207</v>
       </c>
       <c r="B110" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C110" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E110">
         <v>3</v>
@@ -6820,13 +6815,13 @@
         <v>207</v>
       </c>
       <c r="B111" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C111" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E111">
         <v>3</v>
@@ -6837,13 +6832,13 @@
         <v>207</v>
       </c>
       <c r="B112" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C112" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D112" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E112">
         <v>3</v>
@@ -6854,13 +6849,13 @@
         <v>207</v>
       </c>
       <c r="B113" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C113" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D113" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E113">
         <v>3</v>
@@ -6871,13 +6866,13 @@
         <v>207</v>
       </c>
       <c r="B114" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C114" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D114" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E114">
         <v>3</v>
@@ -6888,13 +6883,13 @@
         <v>207</v>
       </c>
       <c r="B115" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C115" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D115" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E115">
         <v>3</v>
@@ -6905,13 +6900,13 @@
         <v>207</v>
       </c>
       <c r="B116" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C116" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D116" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E116">
         <v>2</v>
@@ -6922,13 +6917,13 @@
         <v>206</v>
       </c>
       <c r="B117" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C117" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D117" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E117">
         <v>3</v>
@@ -6939,13 +6934,13 @@
         <v>206</v>
       </c>
       <c r="B118" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C118" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D118" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E118">
         <v>3</v>
@@ -6956,13 +6951,13 @@
         <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D119" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E119">
         <v>3</v>
@@ -6973,13 +6968,13 @@
         <v>206</v>
       </c>
       <c r="B120" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D120" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E120">
         <v>3</v>
@@ -6990,13 +6985,13 @@
         <v>206</v>
       </c>
       <c r="B121" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E121">
         <v>3</v>
@@ -7007,13 +7002,13 @@
         <v>206</v>
       </c>
       <c r="B122" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C122" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D122" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E122">
         <v>3</v>
@@ -7024,13 +7019,13 @@
         <v>206</v>
       </c>
       <c r="B123" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C123" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D123" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E123">
         <v>2</v>
@@ -7041,13 +7036,13 @@
         <v>206</v>
       </c>
       <c r="B124" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C124" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -7058,13 +7053,13 @@
         <v>91</v>
       </c>
       <c r="B125" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C125" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D125" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E125">
         <v>2</v>
@@ -7075,13 +7070,13 @@
         <v>91</v>
       </c>
       <c r="B126" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C126" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D126" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E126">
         <v>2</v>
@@ -7092,13 +7087,13 @@
         <v>91</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D127" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E127">
         <v>2</v>
@@ -7109,13 +7104,13 @@
         <v>91</v>
       </c>
       <c r="B128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C128" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D128" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -7126,13 +7121,13 @@
         <v>91</v>
       </c>
       <c r="B129" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C129" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D129" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E129">
         <v>2</v>
@@ -7143,13 +7138,13 @@
         <v>91</v>
       </c>
       <c r="B130" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D130" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E130">
         <v>2</v>
@@ -7160,13 +7155,13 @@
         <v>91</v>
       </c>
       <c r="B131" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C131" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E131">
         <v>2</v>
@@ -7177,13 +7172,13 @@
         <v>91</v>
       </c>
       <c r="B132" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E132">
         <v>2</v>
@@ -7194,13 +7189,13 @@
         <v>91</v>
       </c>
       <c r="B133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D133" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E133">
         <v>2</v>
@@ -7211,13 +7206,13 @@
         <v>91</v>
       </c>
       <c r="B134" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C134" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D134" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E134">
         <v>2</v>
@@ -7228,13 +7223,13 @@
         <v>91</v>
       </c>
       <c r="B135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C135" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D135" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E135">
         <v>3</v>
@@ -7245,13 +7240,13 @@
         <v>91</v>
       </c>
       <c r="B136" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C136" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D136" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E136">
         <v>3</v>
@@ -7262,13 +7257,13 @@
         <v>91</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C137" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D137" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E137">
         <v>3</v>
@@ -7279,13 +7274,13 @@
         <v>91</v>
       </c>
       <c r="B138" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C138" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D138" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E138">
         <v>2</v>
@@ -7296,13 +7291,13 @@
         <v>91</v>
       </c>
       <c r="B139" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C139" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D139" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E139">
         <v>3</v>
@@ -7313,13 +7308,13 @@
         <v>91</v>
       </c>
       <c r="B140" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C140" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D140" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E140">
         <v>3</v>
@@ -7330,13 +7325,13 @@
         <v>205</v>
       </c>
       <c r="B141" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C141" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E141">
         <v>3</v>
@@ -7347,13 +7342,13 @@
         <v>205</v>
       </c>
       <c r="B142" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C142" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D142" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E142">
         <v>3</v>
@@ -7364,13 +7359,13 @@
         <v>205</v>
       </c>
       <c r="B143" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C143" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D143" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -7381,13 +7376,13 @@
         <v>205</v>
       </c>
       <c r="B144" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C144" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D144" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E144">
         <v>3</v>
@@ -7398,13 +7393,13 @@
         <v>204</v>
       </c>
       <c r="B145" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C145" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D145" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E145">
         <v>3</v>
@@ -7415,13 +7410,13 @@
         <v>204</v>
       </c>
       <c r="B146" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D146" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E146">
         <v>3</v>
@@ -7432,13 +7427,13 @@
         <v>204</v>
       </c>
       <c r="B147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C147" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D147" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E147">
         <v>3</v>
@@ -7449,13 +7444,13 @@
         <v>204</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C148" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D148" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E148">
         <v>3</v>
@@ -7466,13 +7461,13 @@
         <v>204</v>
       </c>
       <c r="B149" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D149" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E149">
         <v>3</v>
@@ -7483,13 +7478,13 @@
         <v>203</v>
       </c>
       <c r="B150" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C150" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D150" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E150">
         <v>3</v>
@@ -7500,13 +7495,13 @@
         <v>202</v>
       </c>
       <c r="B151" t="s">
+        <v>327</v>
+      </c>
+      <c r="C151" t="s">
+        <v>227</v>
+      </c>
+      <c r="D151" t="s">
         <v>328</v>
-      </c>
-      <c r="C151" t="s">
-        <v>228</v>
-      </c>
-      <c r="D151" t="s">
-        <v>329</v>
       </c>
       <c r="E151">
         <v>3</v>
